--- a/assets/constructions/examples/ctd_tgi_radial.xlsx
+++ b/assets/constructions/examples/ctd_tgi_radial.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,86 +609,110 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A32SWMTEL0519M</t>
+          <t>VGIR-25-31-2C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>VG-Cut</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WID_WMT..05</t>
+          <t>VAR_VGI25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>9.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ISO_5609:32</t>
+          <t>ISO_5609:25</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>WIDIA_WMT:05</t>
+          <t>VARGUS_VGD:2</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>90</v>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>50</v>
+      </c>
       <c r="S2" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="T2" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="b">
@@ -720,14 +744,28 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2020/ widia токарный инструмент</t>
-        </is>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>522.2</v>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>48007.78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MGIVR3732-5</t>
+          <t>MGIVL2520-3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -738,7 +776,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LIK_MG/R500W</t>
+          <t>LIK_MG/R300W</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -747,16 +785,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ISO_5609:32</t>
+          <t>ISO_5609:20</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>LIKON_MG/R500W</t>
+          <t>LIKON_MG/R300W</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -767,7 +805,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -777,30 +815,30 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="S3" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="T3" t="n">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="n">
-        <v>21.5</v>
+        <v>15.6</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
@@ -833,71 +871,83 @@
           <t>2022/LIKON Инструментальный каталог</t>
         </is>
       </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MGIVL2520-4</t>
+          <t>VGIR-32-39-4C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LIKON</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>VARGUS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VG-Cut</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LIK_MG/R400W</t>
+          <t>VAR_VGI32</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ISO_5609:20</t>
+          <t>ISO_5609:32</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>LIKON_MG/R400W</t>
+          <t>VARGUS_VGD:4</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>90</v>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="T4" t="n">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
@@ -910,10 +960,12 @@
         <v>4</v>
       </c>
       <c r="Y4" t="n">
-        <v>15.6</v>
+        <v>27.5</v>
       </c>
       <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
       <c r="AB4" t="b">
         <v>0</v>
       </c>
@@ -940,53 +992,69 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
-        </is>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>605.78</v>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>55691.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A20SWMTEL0519N</t>
+          <t>VGIL-40-50-6C</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>VG-Cut</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WID_WMT..05</t>
+          <t>VAR_VGI40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ISO_5609:31.75</t>
+          <t>ISO_5609:40</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>WIDIA_WMT:05</t>
+          <t>VARGUS_VGD:6</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>90</v>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
@@ -995,34 +1063,36 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>31.75</v>
+        <v>40</v>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>80</v>
+      </c>
       <c r="S5" t="n">
-        <v>46.99</v>
+        <v>50</v>
       </c>
       <c r="T5" t="n">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>4.78</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>4.78</v>
+        <v>6</v>
       </c>
       <c r="X5" t="n">
-        <v>4.78</v>
+        <v>6</v>
       </c>
       <c r="Y5" t="n">
-        <v>29.01</v>
+        <v>30.5</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="b">
@@ -1054,55 +1124,63 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2020/ widia токарный инструмент</t>
-        </is>
+          <t>2019 / Groovex Catalog</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>711.15</v>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>65378.65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VGIR-20-24-3C</t>
+          <t>MGIVR3125-5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>VG-Cut</t>
-        </is>
-      </c>
+          <t>LIKON</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VAR_VGI20</t>
+          <t>LIK_MG/R500W</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>LIKON</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ISO_5609:20</t>
+          <t>ISO_5609:25</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>VARGUS_VGD:3</t>
+          <t>LIKON_MG/R500W</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>90</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
@@ -1111,41 +1189,39 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="S6" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="T6" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y6" t="n">
-        <v>17.5</v>
+        <v>19.4</v>
       </c>
       <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="b">
         <v>0</v>
       </c>
@@ -1172,9 +1248,15 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2019 / Groovex Catalog</t>
-        </is>
-      </c>
+          <t>2022/LIKON Инструментальный каталог</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
